--- a/结题/新建 Microsoft Excel 工作表.xlsx
+++ b/结题/新建 Microsoft Excel 工作表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\zjuthesis\结题\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF27C90A-B38F-430B-9E77-60D412A93466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50906CE1-572C-450A-9CF4-94F8F5DC4975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="180" formatCode="0.0%"/>
+    <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -125,7 +125,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
@@ -325,6 +325,48 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="6.585992567799347E-17"/>
+                  <c:y val="3.2857324699704628E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-F2B8-45B6-8CA6-52128E0FE80F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0"/>
+                  <c:y val="4.6000254579586647E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-F2B8-45B6-8CA6-52128E0FE80F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -525,6 +567,48 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="6.585992567799347E-17"/>
+                  <c:y val="-1.3142929879881899E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-F2B8-45B6-8CA6-52128E0FE80F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0"/>
+                  <c:y val="-4.9285987049557126E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-F2B8-45B6-8CA6-52128E0FE80F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -579,6 +663,30 @@
               </c:ext>
             </c:extLst>
           </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$I$9:$I$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>256</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>512</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1024</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4096</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Sheet1!$K$9:$K$13</c:f>
@@ -586,19 +694,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>8.4</c:v>
+                  <c:v>8.6999999999999993</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.3899999999999997</c:v>
+                  <c:v>4.4400000000000004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.3199999999999998</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.23</c:v>
+                  <c:v>1.27</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.23</c:v>
+                  <c:v>0.64</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -607,108 +715,6 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000004-BDCA-4955-B629-D663894714CD}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$L$8</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>GPU时间</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="34925" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="6"/>
-            <c:spPr>
-              <a:gradFill rotWithShape="1">
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent4">
-                      <a:satMod val="103000"/>
-                      <a:lumMod val="102000"/>
-                      <a:tint val="94000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="50000">
-                    <a:schemeClr val="accent4">
-                      <a:satMod val="110000"/>
-                      <a:lumMod val="100000"/>
-                      <a:shade val="100000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent4">
-                      <a:lumMod val="99000"/>
-                      <a:satMod val="120000"/>
-                      <a:shade val="78000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                  <a:srgbClr val="000000">
-                    <a:alpha val="63000"/>
-                  </a:srgbClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$L$9:$L$13</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>39.200000000000003</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>39.200000000000003</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>31.9</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>26.6</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-BDCA-4955-B629-D663894714CD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -995,10 +1001,12 @@
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1343579023"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -1965,32 +1973,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="I4:P13"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="15" max="15" width="16.6640625" customWidth="1"/>
+    <col min="15" max="15" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="9:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="9:16" x14ac:dyDescent="0.2">
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="9:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="9:16" x14ac:dyDescent="0.2">
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="4"/>
     </row>
-    <row r="6" spans="9:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="9:16" x14ac:dyDescent="0.2">
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="9:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="9:16" x14ac:dyDescent="0.2">
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="4"/>
     </row>
-    <row r="8" spans="9:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="9:16" x14ac:dyDescent="0.2">
       <c r="I8" s="1" t="s">
         <v>2</v>
       </c>
@@ -2016,7 +2024,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="9:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="9:16" x14ac:dyDescent="0.2">
       <c r="I9" s="1">
         <v>256</v>
       </c>
@@ -2024,27 +2032,27 @@
         <v>0.185</v>
       </c>
       <c r="K9" s="1">
-        <v>8.4</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="L9" s="3">
-        <v>39.200000000000003</v>
+        <v>38.5</v>
       </c>
       <c r="M9" s="3">
-        <v>50.9</v>
+        <v>49.4</v>
       </c>
       <c r="N9" s="4">
         <f>M9-L9</f>
-        <v>11.699999999999996</v>
+        <v>10.899999999999999</v>
       </c>
       <c r="O9" s="1">
         <f>N9-K9</f>
-        <v>3.2999999999999954</v>
+        <v>2.1999999999999993</v>
       </c>
       <c r="P9" s="1">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
     </row>
-    <row r="10" spans="9:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="9:16" x14ac:dyDescent="0.2">
       <c r="I10" s="1">
         <v>512</v>
       </c>
@@ -2052,27 +2060,27 @@
         <v>0.14899999999999999</v>
       </c>
       <c r="K10" s="1">
-        <v>4.3899999999999997</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="L10" s="3">
-        <v>39.200000000000003</v>
+        <v>38.4</v>
       </c>
       <c r="M10" s="3">
-        <v>46.2</v>
+        <v>44.5</v>
       </c>
       <c r="N10" s="4">
         <f t="shared" ref="N10:N12" si="0">M10-L10</f>
-        <v>7</v>
+        <v>6.1000000000000014</v>
       </c>
       <c r="O10" s="1">
         <f t="shared" ref="O10:O12" si="1">N10-K10</f>
-        <v>2.6100000000000003</v>
+        <v>1.660000000000001</v>
       </c>
       <c r="P10" s="1">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
     </row>
-    <row r="11" spans="9:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="9:16" x14ac:dyDescent="0.2">
       <c r="I11" s="1">
         <v>1024</v>
       </c>
@@ -2080,27 +2088,27 @@
         <v>0.114</v>
       </c>
       <c r="K11" s="1">
-        <v>2.3199999999999998</v>
+        <v>2.5</v>
       </c>
       <c r="L11" s="3">
-        <v>31.9</v>
+        <v>36</v>
       </c>
       <c r="M11" s="3">
-        <v>36.6</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="N11" s="4">
         <f t="shared" si="0"/>
-        <v>4.7000000000000028</v>
+        <v>3.7999999999999972</v>
       </c>
       <c r="O11" s="1">
         <f t="shared" si="1"/>
-        <v>2.380000000000003</v>
+        <v>1.2999999999999972</v>
       </c>
       <c r="P11" s="1">
-        <v>7.0000000000000007E-2</v>
+        <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="9:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="9:16" x14ac:dyDescent="0.2">
       <c r="I12" s="1">
         <v>2048</v>
       </c>
@@ -2108,27 +2116,27 @@
         <v>8.8999999999999996E-2</v>
       </c>
       <c r="K12" s="1">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="L12" s="1">
-        <v>26.6</v>
+        <v>31.4</v>
       </c>
       <c r="M12" s="4">
-        <v>30.3</v>
+        <v>33.9</v>
       </c>
       <c r="N12" s="4">
         <f t="shared" si="0"/>
-        <v>3.6999999999999993</v>
+        <v>2.5</v>
       </c>
       <c r="O12" s="1">
         <f t="shared" si="1"/>
-        <v>2.4699999999999993</v>
+        <v>1.23</v>
       </c>
       <c r="P12" s="1">
-        <v>0.04</v>
+        <v>0.17</v>
       </c>
     </row>
-    <row r="13" spans="9:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="9:16" x14ac:dyDescent="0.2">
       <c r="I13" s="1">
         <v>4096</v>
       </c>
@@ -2136,14 +2144,14 @@
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="K13" s="1">
-        <v>1.23</v>
+        <v>0.64</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1">
-        <v>0.69</v>
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>
